--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.07296399479585</v>
+        <v>2.611856649154325</v>
       </c>
       <c r="D2" t="n">
-        <v>16.25702579491557</v>
+        <v>2.641766691673781</v>
       </c>
       <c r="E2" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F2" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.70952860748611</v>
+        <v>3.202798398716494</v>
       </c>
       <c r="D3" t="n">
-        <v>19.92043795620329</v>
+        <v>3.237071167883035</v>
       </c>
       <c r="E3" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F3" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.41686252693261</v>
+        <v>2.83024016062655</v>
       </c>
       <c r="D4" t="n">
-        <v>17.07321715923349</v>
+        <v>2.774397788375442</v>
       </c>
       <c r="E4" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F4" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.59303836219366</v>
+        <v>4.158868733856471</v>
       </c>
       <c r="D5" t="n">
-        <v>26.60010423764827</v>
+        <v>4.322516938617845</v>
       </c>
       <c r="E5" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F5" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.44838048416074</v>
+        <v>4.135361828676121</v>
       </c>
       <c r="D6" t="n">
-        <v>26.03549292842331</v>
+        <v>4.230767600868789</v>
       </c>
       <c r="E6" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F6" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.89331347238337</v>
+        <v>3.557663439262297</v>
       </c>
       <c r="D7" t="n">
-        <v>22.92257490156969</v>
+        <v>3.724918421505074</v>
       </c>
       <c r="E7" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F7" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.69696508534197</v>
+        <v>2.225756826368071</v>
       </c>
       <c r="D8" t="n">
-        <v>12.75753354181203</v>
+        <v>2.073099200544456</v>
       </c>
       <c r="E8" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F8" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.9783392741444</v>
+        <v>4.221480132048464</v>
       </c>
       <c r="D9" t="n">
-        <v>25.15949757539827</v>
+        <v>4.088418356002219</v>
       </c>
       <c r="E9" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F9" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.73339688358574</v>
+        <v>4.181676993582683</v>
       </c>
       <c r="D10" t="n">
-        <v>24.84047118366265</v>
+        <v>4.036576567345181</v>
       </c>
       <c r="E10" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F10" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.16786452406879</v>
+        <v>4.902277985161178</v>
       </c>
       <c r="D11" t="n">
-        <v>30.90449879142445</v>
+        <v>5.021981053606473</v>
       </c>
       <c r="E11" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F11" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>3.523024180290055</v>
+        <v>0.572491429297134</v>
       </c>
       <c r="D12" t="n">
-        <v>3.630979038539373</v>
+        <v>0.5900340937626481</v>
       </c>
       <c r="E12" t="n">
-        <v>7.182408141081813</v>
+        <v>1.167141322925795</v>
       </c>
       <c r="F12" t="n">
-        <v>7.367522811036999</v>
+        <v>1.197222456793512</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
